--- a/offers/seasonal/عروض اليوم الوطني بيوديرما وسنسوداين.xlsx
+++ b/offers/seasonal/عروض اليوم الوطني بيوديرما وسنسوداين.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98FBC94-A3E4-4B3C-8745-73C09256B8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14036A1D-AF92-4839-810F-9C1CBAB86D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -43,33 +43,18 @@
     <t>نوع العرض</t>
   </si>
   <si>
-    <t>00038758</t>
-  </si>
-  <si>
     <t>Photoderm Xdfnse Ultra-Fld Sp50+ Inv40Ml</t>
   </si>
   <si>
-    <t>00038759</t>
-  </si>
-  <si>
     <t>Photoderm Xdfnse Ultr-Fldsp50+ Tnt1 40Ml</t>
   </si>
   <si>
-    <t>00038760</t>
-  </si>
-  <si>
     <t>Photoderm Xdfnse Ultr-Fldsp50+ Tnt2 40Ml</t>
   </si>
   <si>
-    <t>00038761</t>
-  </si>
-  <si>
     <t>Photoderm Xdfnse Ultr-Fldsp50+ Tnt3 40Ml</t>
   </si>
   <si>
-    <t>00038762</t>
-  </si>
-  <si>
     <t>Photoderm Xdfnse Ultr-Fldsp50+ Tnt4 40Ml</t>
   </si>
   <si>
@@ -79,73 +64,37 @@
     <t>كمية</t>
   </si>
   <si>
-    <t>00018369</t>
-  </si>
-  <si>
     <t>بارودونتكس غسول فم انتعاش زائد 500 مل(73571) 9301</t>
   </si>
   <si>
-    <t>0007322</t>
-  </si>
-  <si>
     <t>بارودونتكس معجون اسنان انتعاش زائد75مل(73701) 3327</t>
   </si>
   <si>
-    <t>00023346</t>
-  </si>
-  <si>
     <t>بارودونتكس معجون للثة+النفس والحساسية 75 مل(73686) 847</t>
   </si>
   <si>
-    <t>00023347</t>
-  </si>
-  <si>
     <t>بارودونتكس معجون والحساسيةتبييض75مل(73687) 3830</t>
   </si>
   <si>
-    <t>00033991</t>
-  </si>
-  <si>
     <t>سنسوداين فرشاة اسنان اطفال  (+6) 121336</t>
   </si>
   <si>
-    <t>0008083</t>
-  </si>
-  <si>
     <t>سنسوداين معجوان اسنان (عبوة 2حبة )عناية متعدة</t>
   </si>
   <si>
-    <t>00039248</t>
-  </si>
-  <si>
     <t>سنسوداين معجون اسنان كلينيكال تنظيف عميق 75 مل 1930</t>
   </si>
   <si>
-    <t>0008036</t>
-  </si>
-  <si>
     <t>سنسوداين معجون انتعاش زائد 75 مل كود 6027</t>
   </si>
   <si>
-    <t>00025034</t>
-  </si>
-  <si>
     <t>سنسوداين معجون حماية متكاملة تبييض مطور 75 مل 3762</t>
   </si>
   <si>
-    <t>00025033</t>
-  </si>
-  <si>
     <t>سنسوداين معجون حماية متكاملة نفس منعش 75 مل 3779</t>
   </si>
   <si>
-    <t>0008111</t>
-  </si>
-  <si>
     <t>سنسوداين معجون واقي المينا+اطفال 50 مل 500358</t>
-  </si>
-  <si>
-    <t>00039249</t>
   </si>
   <si>
     <t>سنسوداين</t>
@@ -216,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -235,6 +184,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -610,17 +560,17 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8">
+        <v>38758</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C2" s="3">
         <v>141.44999999999999</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4">
         <v>46295</v>
@@ -629,21 +579,21 @@
         <v>46272</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
+      <c r="A3" s="8">
+        <v>38759</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3">
         <v>141.44999999999999</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4">
         <v>46295</v>
@@ -652,21 +602,21 @@
         <v>46272</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
+      <c r="A4" s="8">
+        <v>38760</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3">
         <v>141.44999999999999</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4" s="4">
         <v>46295</v>
@@ -675,21 +625,21 @@
         <v>46272</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
+      <c r="A5" s="8">
+        <v>38761</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <v>141.44999999999999</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E5" s="4">
         <v>46295</v>
@@ -698,21 +648,21 @@
         <v>46272</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
+      <c r="A6" s="8">
+        <v>38762</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>141.44999999999999</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" s="4">
         <v>46295</v>
@@ -721,15 +671,15 @@
         <v>46272</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
+      <c r="A7" s="8">
+        <v>18369</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3">
         <v>31.9</v>
@@ -744,15 +694,15 @@
         <v>46272</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
+      <c r="A8" s="8">
+        <v>7322</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3">
         <v>34.04</v>
@@ -767,15 +717,15 @@
         <v>46272</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
+      <c r="A9" s="8">
+        <v>23346</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3">
         <v>39.79</v>
@@ -790,15 +740,15 @@
         <v>46272</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+      <c r="A10" s="8">
+        <v>23347</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3">
         <v>39.79</v>
@@ -813,15 +763,15 @@
         <v>46272</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
+      <c r="A11" s="8">
+        <v>33991</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3">
         <v>16.7</v>
@@ -836,15 +786,15 @@
         <v>46272</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
+      <c r="A12" s="8">
+        <v>8083</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3">
         <v>49.15</v>
@@ -859,15 +809,15 @@
         <v>46272</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
+      <c r="A13" s="8">
+        <v>39248</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>49.8</v>
@@ -882,15 +832,15 @@
         <v>46272</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
+      <c r="A14" s="8">
+        <v>8036</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3">
         <v>29.9</v>
@@ -905,15 +855,15 @@
         <v>46272</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
+      <c r="A15" s="8">
+        <v>25034</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3">
         <v>39.1</v>
@@ -928,15 +878,15 @@
         <v>46272</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>37</v>
+      <c r="A16" s="8">
+        <v>25033</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3">
         <v>39.1</v>
@@ -951,15 +901,15 @@
         <v>46272</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>39</v>
+      <c r="A17" s="8">
+        <v>8111</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3">
         <v>26.35</v>
@@ -974,15 +924,15 @@
         <v>46272</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+      <c r="A18" s="8">
+        <v>39249</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C18" s="3">
         <v>49.8</v>
@@ -997,7 +947,7 @@
         <v>46272</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
